--- a/docs/Project 2 Plan.xlsx
+++ b/docs/Project 2 Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57bb492ad5be0872/Desktop/School/CS-2430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5CE59F9-2C58-450F-BA78-DD3AE0C6ACB6}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="1" activeTab="1" xr2:uid="{34D08FD4-51C7-4A98-AE26-ECA49DBE509F}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Tasks &amp; Milestones" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="89">
   <si>
     <t>Group 2 Project 1: Set Operations</t>
   </si>
@@ -105,9 +106,6 @@
     <t>CSIS 2430 - 502</t>
   </si>
   <si>
-    <t>Group meeting 3</t>
-  </si>
-  <si>
     <t>Tasks and Milestones</t>
   </si>
   <si>
@@ -280,6 +278,33 @@
   </si>
   <si>
     <t>Part 4 Code</t>
+  </si>
+  <si>
+    <t>Meeting 3</t>
+  </si>
+  <si>
+    <t>Project Scope</t>
+  </si>
+  <si>
+    <t>Commit: abe508908d991dc4e0316e9703f2fd3919fd3001</t>
+  </si>
+  <si>
+    <t>Commit: 9e3c761ad1351c342bed733109f54d97e81f00fe</t>
+  </si>
+  <si>
+    <t>Commit: 6e0303585ead7418220c1b7ede9e210104838d30</t>
+  </si>
+  <si>
+    <t>Commit: 7392e70057701b17c21dfc0b4a10bcb2a66f8195</t>
+  </si>
+  <si>
+    <t>Commit: 20451d3bd044280e478a959ef5ce325c571250be</t>
+  </si>
+  <si>
+    <t>Commit: 938aaf9d9abb09484976ad421a0badf3df3cf638</t>
+  </si>
+  <si>
+    <t>Commit: 0f2f32f0f8939e76d6c95517528df3be46dfe1ab</t>
   </si>
 </sst>
 </file>
@@ -442,7 +467,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -500,15 +525,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
@@ -526,7 +542,15 @@
     <xf numFmtId="14" fontId="6" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1311,10 +1335,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}" name="Table2" displayName="Table2" ref="A16:G30" totalsRowShown="0" headerRowDxfId="39">
-  <autoFilter ref="A16:G30" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:G30">
-    <sortCondition ref="C16:C30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}" name="Table2" displayName="Table2" ref="A16:G31" totalsRowShown="0" headerRowDxfId="39">
+  <autoFilter ref="A16:G31" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:G31">
+    <sortCondition ref="C16:C31"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F4C66F6C-4C65-456B-B1F2-3BC3F82DB741}" name="Item" dataDxfId="38"/>
@@ -1346,8 +1370,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}" name="Table4" displayName="Table4" ref="A34:G49" totalsRowShown="0" headerRowDxfId="20">
-  <autoFilter ref="A34:G49" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}" name="Table4" displayName="Table4" ref="A35:G49" totalsRowShown="0" headerRowDxfId="20">
+  <autoFilter ref="A35:G49" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3EBAA60D-CE23-4567-B518-864EBB94F1CB}" name="Item" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{3D024BB8-4ABA-4BE7-9C4D-31667FEF5FAB}" name="Assigned" dataDxfId="18"/>
@@ -1703,25 +1727,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1801,37 +1825,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1840,15 +1864,15 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
+      <c r="A5" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
@@ -1861,38 +1885,40 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="C7" s="5">
         <v>46089</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46087</v>
+      </c>
       <c r="F7" s="10"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
@@ -1900,8 +1926,8 @@
       <c r="C8" s="5">
         <v>46096</v>
       </c>
-      <c r="D8" s="30" t="s">
-        <v>62</v>
+      <c r="D8" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="22"/>
@@ -1909,16 +1935,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5">
         <v>46096</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>62</v>
+      <c r="D9" s="28" t="s">
+        <v>61</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="10"/>
@@ -1926,16 +1952,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="5">
         <v>46103</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>62</v>
+      <c r="D10" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="22"/>
@@ -1943,7 +1969,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -1951,8 +1977,8 @@
       <c r="C11" s="5">
         <v>46103</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>62</v>
+      <c r="D11" s="28" t="s">
+        <v>61</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="22"/>
@@ -1960,16 +1986,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5">
         <v>46103</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="10"/>
@@ -1984,15 +2010,15 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="A15" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
@@ -2005,21 +2031,21 @@
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>20</v>
@@ -2028,7 +2054,7 @@
         <v>46083</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="11">
         <v>46083</v>
@@ -2038,7 +2064,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>20</v>
@@ -2047,7 +2073,7 @@
         <v>46083</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="5">
         <v>46083</v>
@@ -2057,7 +2083,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
@@ -2066,9 +2092,11 @@
         <v>46085</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E19" s="5">
+        <v>46083</v>
+      </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -2082,14 +2110,19 @@
         <v>46085</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46085</v>
+      </c>
       <c r="F20" s="10"/>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
@@ -2098,39 +2131,59 @@
         <v>46089</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E21" s="5">
+        <v>46090</v>
+      </c>
       <c r="F21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46095</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="5">
+        <v>46090</v>
+      </c>
       <c r="F22" s="10"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="5">
+        <v>46095</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="10"/>
+      <c r="F23" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -2141,7 +2194,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
@@ -2152,7 +2205,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
@@ -2163,28 +2216,28 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="10"/>
       <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="10"/>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
@@ -2195,7 +2248,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -2204,145 +2257,147 @@
       <c r="F30" s="10"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A33" s="27" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="5">
+      <c r="E36" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7">
         <v>46089</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="7">
-        <v>46089</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="8"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="5">
-        <v>46089</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="4"/>
+      <c r="D37" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="5">
+        <v>46085</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C39" s="5">
         <v>46096</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="7">
+      <c r="D39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="7">
         <v>46089</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46089</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="4"/>
+      <c r="D40" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4</v>
@@ -2351,32 +2406,40 @@
         <v>46089</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E41" s="5">
+        <v>46090</v>
+      </c>
       <c r="F41" s="10"/>
-      <c r="G41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42" s="5">
         <v>46089</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E42" s="5">
+        <v>46090</v>
+      </c>
       <c r="F42" s="10"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>6</v>
@@ -2385,77 +2448,91 @@
         <v>46089</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E43" s="5">
+        <v>46090</v>
+      </c>
       <c r="F43" s="10"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
-        <v>36</v>
+      <c r="A44" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C45" s="5">
         <v>46096</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A45" s="35" t="s">
+      <c r="D45" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="39">
+        <v>46096</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="30"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="29"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="42">
+      <c r="B47" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="38">
         <v>46096</v>
       </c>
-      <c r="D45" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" s="33"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="32"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A46" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18">
-        <v>46096</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="18"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="17"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A47" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="39"/>
-      <c r="C47" s="41">
-        <v>46096</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="36"/>
+      <c r="D47" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="34"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="33"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="17" t="s">
         <v>20</v>
@@ -2464,7 +2541,7 @@
         <v>46096</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="25"/>
@@ -2472,7 +2549,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>6</v>
@@ -2481,7 +2558,7 @@
         <v>46103</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="25"/>
@@ -2494,15 +2571,15 @@
       <c r="E50" s="3"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
+      <c r="A52" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
@@ -2515,21 +2592,21 @@
         <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -2540,7 +2617,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
@@ -2551,7 +2628,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
@@ -2562,7 +2639,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
@@ -2573,7 +2650,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
@@ -2584,7 +2661,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
@@ -2595,7 +2672,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
@@ -2606,7 +2683,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -2617,7 +2694,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
@@ -2628,7 +2705,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
@@ -2639,7 +2716,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
@@ -2650,7 +2727,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
@@ -2661,7 +2738,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
@@ -2684,7 +2761,7 @@
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>

--- a/docs/Project 2 Plan.xlsx
+++ b/docs/Project 2 Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57bb492ad5be0872/Desktop/School/CS-2430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5CE59F9-2C58-450F-BA78-DD3AE0C6ACB6}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D5B653-360F-473D-B092-1B45A88B141D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="1" activeTab="1" xr2:uid="{34D08FD4-51C7-4A98-AE26-ECA49DBE509F}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Tasks &amp; Milestones" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="87">
   <si>
     <t>Group 2 Project 1: Set Operations</t>
   </si>
@@ -175,42 +174,9 @@
     <t>Introduction</t>
   </si>
   <si>
-    <t>Implementation Methods - Ordinary sets</t>
-  </si>
-  <si>
-    <t>Implementation Methods - multisets</t>
-  </si>
-  <si>
-    <t>Verification Approach</t>
-  </si>
-  <si>
-    <t>Discussion - 1</t>
-  </si>
-  <si>
-    <t>Discussion - 2</t>
-  </si>
-  <si>
-    <t>Discussion - 3</t>
-  </si>
-  <si>
-    <t>Discussion - 4</t>
-  </si>
-  <si>
-    <t>Discussion - 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discussion - 6 </t>
-  </si>
-  <si>
-    <t>Lessons learned</t>
-  </si>
-  <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Conclusion</t>
-  </si>
-  <si>
     <t>README documentation</t>
   </si>
   <si>
@@ -305,6 +271,33 @@
   </si>
   <si>
     <t>Commit: 0f2f32f0f8939e76d6c95517528df3be46dfe1ab</t>
+  </si>
+  <si>
+    <t>Algorithm Summaries</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>Discussion-1</t>
+  </si>
+  <si>
+    <t>Discussion-2</t>
+  </si>
+  <si>
+    <t>Discussion-3</t>
+  </si>
+  <si>
+    <t>Discussion-4</t>
+  </si>
+  <si>
+    <t>Discussion-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusion </t>
+  </si>
+  <si>
+    <t>Lessons Learnd</t>
   </si>
 </sst>
 </file>
@@ -1320,6 +1313,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1837,7 +1834,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="41" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
@@ -1899,10 +1896,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5">
         <v>46089</v>
@@ -1918,7 +1915,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
@@ -1927,7 +1924,7 @@
         <v>46096</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="22"/>
@@ -1935,16 +1932,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5">
         <v>46096</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="10"/>
@@ -1952,16 +1949,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5">
         <v>46103</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="22"/>
@@ -1969,7 +1966,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -1978,7 +1975,7 @@
         <v>46103</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="22"/>
@@ -1986,16 +1983,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5">
         <v>46103</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="10"/>
@@ -2045,7 +2042,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>20</v>
@@ -2064,7 +2061,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>20</v>
@@ -2083,7 +2080,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
@@ -2117,12 +2114,12 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
@@ -2137,13 +2134,13 @@
         <v>46090</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>8</v>
@@ -2159,12 +2156,12 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
@@ -2173,11 +2170,13 @@
         <v>46095</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="E23" s="5">
+        <v>46090</v>
+      </c>
       <c r="F23" s="10" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -2304,7 +2303,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>4</v>
@@ -2320,7 +2319,7 @@
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="4" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
@@ -2334,7 +2333,7 @@
         <v>46089</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="23"/>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -2372,7 +2371,7 @@
         <v>46096</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="10"/>
@@ -2383,13 +2382,13 @@
         <v>24</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C40" s="7">
         <v>46089</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E40" s="16"/>
       <c r="F40" s="24"/>
@@ -2397,7 +2396,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4</v>
@@ -2413,12 +2412,12 @@
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>4</v>
@@ -2434,12 +2433,12 @@
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>6</v>
@@ -2455,12 +2454,12 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>6</v>
@@ -2476,7 +2475,7 @@
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
@@ -2490,7 +2489,7 @@
         <v>46096</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="10"/>
@@ -2498,7 +2497,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="32" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B46" s="32" t="s">
         <v>8</v>
@@ -2507,15 +2506,17 @@
         <v>46096</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="30"/>
+        <v>34</v>
+      </c>
+      <c r="E46" s="30">
+        <v>46096</v>
+      </c>
       <c r="F46" s="31"/>
       <c r="G46" s="29"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="36" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B47" s="36" t="s">
         <v>4</v>
@@ -2524,9 +2525,11 @@
         <v>46096</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="34"/>
+        <v>34</v>
+      </c>
+      <c r="E47" s="34">
+        <v>46096</v>
+      </c>
       <c r="F47" s="35"/>
       <c r="G47" s="33"/>
     </row>
@@ -2541,7 +2544,7 @@
         <v>46096</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="25"/>
@@ -2549,7 +2552,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>6</v>
@@ -2558,7 +2561,7 @@
         <v>46103</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="25"/>
@@ -2617,7 +2620,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
@@ -2628,7 +2631,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
@@ -2639,7 +2642,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
@@ -2650,7 +2653,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="20" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="20" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
@@ -2672,7 +2675,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="20" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
@@ -2683,7 +2686,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -2694,7 +2697,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="20" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
@@ -2705,7 +2708,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="20" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="20" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
@@ -2726,9 +2729,7 @@
       <c r="G64" s="4"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A65" s="20" t="s">
-        <v>56</v>
-      </c>
+      <c r="A65" s="20"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -2737,9 +2738,7 @@
       <c r="G65" s="4"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A66" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>

--- a/docs/Project 2 Plan.xlsx
+++ b/docs/Project 2 Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57bb492ad5be0872/Desktop/School/CS-2430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D5B653-360F-473D-B092-1B45A88B141D}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A5445A-8D9B-4515-9419-6466EB63C29F}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="1" activeTab="1" xr2:uid="{34D08FD4-51C7-4A98-AE26-ECA49DBE509F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
   <si>
     <t>Group 2 Project 1: Set Operations</t>
   </si>
@@ -117,9 +117,6 @@
     <t>Report Outline</t>
   </si>
   <si>
-    <t>Assign report sections</t>
-  </si>
-  <si>
     <t>Plan screencast logistics</t>
   </si>
   <si>
@@ -159,18 +156,12 @@
     <t>Status Date</t>
   </si>
   <si>
-    <t>Record Screencast</t>
-  </si>
-  <si>
     <t>Final code merged on main branch</t>
   </si>
   <si>
     <t>Report Writing Assignments</t>
   </si>
   <si>
-    <t>Screencast planning meeting</t>
-  </si>
-  <si>
     <t>Introduction</t>
   </si>
   <si>
@@ -298,6 +289,42 @@
   </si>
   <si>
     <t>Lessons Learnd</t>
+  </si>
+  <si>
+    <t>Contributions Outline</t>
+  </si>
+  <si>
+    <t>Report summary</t>
+  </si>
+  <si>
+    <t>Saturday 7:00pm</t>
+  </si>
+  <si>
+    <t>Commit: 88c71e776d8195de46ff34ecdc2bdb1d25930e2d</t>
+  </si>
+  <si>
+    <t>Commit: 20c2f439db54f202c5fe416ec6a81eb660482410</t>
+  </si>
+  <si>
+    <t>Commit: 2ab3251fa9b2d9b7ea4fde9390ed53485f65c286</t>
+  </si>
+  <si>
+    <t>Screencast Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Screencast Project Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Screencast Comparisons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Screencast Permutation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Screencast Live run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Screencast Brief Summary</t>
   </si>
 </sst>
 </file>
@@ -460,7 +487,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,7 +520,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -520,14 +546,10 @@
     <xf numFmtId="14" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -544,6 +566,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1332,10 +1355,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}" name="Table2" displayName="Table2" ref="A16:G31" totalsRowShown="0" headerRowDxfId="39">
-  <autoFilter ref="A16:G31" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:G31">
-    <sortCondition ref="C16:C31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}" name="Table2" displayName="Table2" ref="A16:G36" totalsRowShown="0" headerRowDxfId="39">
+  <autoFilter ref="A16:G36" xr:uid="{92FD6656-9EEA-4925-8CC6-333BF0C915F8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:G36">
+    <sortCondition ref="C16:C36"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F4C66F6C-4C65-456B-B1F2-3BC3F82DB741}" name="Item" dataDxfId="38"/>
@@ -1367,8 +1390,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}" name="Table4" displayName="Table4" ref="A35:G49" totalsRowShown="0" headerRowDxfId="20">
-  <autoFilter ref="A35:G49" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}" name="Table4" displayName="Table4" ref="A40:G54" totalsRowShown="0" headerRowDxfId="20">
+  <autoFilter ref="A40:G54" xr:uid="{00D715EC-4533-413F-A354-338857D1B676}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3EBAA60D-CE23-4567-B518-864EBB94F1CB}" name="Item" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{3D024BB8-4ABA-4BE7-9C4D-31667FEF5FAB}" name="Assigned" dataDxfId="18"/>
@@ -1383,8 +1406,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E345B882-2AE3-4D3C-96F9-F47312E2AEDD}" name="Table46" displayName="Table46" ref="A53:G67" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A53:G67" xr:uid="{E345B882-2AE3-4D3C-96F9-F47312E2AEDD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E345B882-2AE3-4D3C-96F9-F47312E2AEDD}" name="Table46" displayName="Table46" ref="A58:G69" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A58:G69" xr:uid="{E345B882-2AE3-4D3C-96F9-F47312E2AEDD}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A987DE21-44F7-4C2B-B179-659CFD58E065}" name="Item" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{5C73A7A9-D3E9-4DC6-880B-7D8A164C9C30}" name="Assigned" dataDxfId="10"/>
@@ -1724,25 +1747,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1810,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A174C0FD-48BE-40EA-A790-3B7853B980F6}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="37.07421875" customWidth="1"/>
@@ -1822,37 +1845,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="A2" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1861,15 +1884,15 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
+      <c r="A5" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
@@ -1882,30 +1905,30 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5">
         <v>46089</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5">
         <v>46087</v>
@@ -1915,7 +1938,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
@@ -1923,50 +1946,54 @@
       <c r="C8" s="5">
         <v>46096</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="22"/>
+      <c r="D8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="5">
+        <v>46096</v>
+      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C9" s="5">
         <v>46096</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="5"/>
+      <c r="D9" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46096</v>
+      </c>
       <c r="F9" s="10"/>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C10" s="5">
         <v>46103</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>50</v>
+      <c r="D10" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="22"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -1974,25 +2001,25 @@
       <c r="C11" s="5">
         <v>46103</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>50</v>
+      <c r="D11" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="22"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5">
         <v>46103</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>50</v>
+      <c r="D12" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="10"/>
@@ -2007,15 +2034,15 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
@@ -2028,21 +2055,21 @@
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>20</v>
@@ -2051,7 +2078,7 @@
         <v>46083</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" s="11">
         <v>46083</v>
@@ -2061,7 +2088,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>20</v>
@@ -2070,7 +2097,7 @@
         <v>46083</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="5">
         <v>46083</v>
@@ -2080,7 +2107,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
@@ -2089,7 +2116,7 @@
         <v>46085</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5">
         <v>46083</v>
@@ -2107,19 +2134,19 @@
         <v>46085</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="5">
         <v>46085</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
@@ -2128,275 +2155,320 @@
         <v>46089</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" s="5">
         <v>46090</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="5">
         <v>46090</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="5">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E23" s="5">
-        <v>46090</v>
+        <v>46096</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46096</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="5">
+        <v>46096</v>
+      </c>
       <c r="F24" s="10"/>
       <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5">
+        <v>46097</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="10"/>
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="10"/>
       <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="4"/>
+      <c r="A27" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46102</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="10"/>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="10"/>
       <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="10"/>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+        <v>94</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E31" s="5"/>
       <c r="F31" s="10"/>
       <c r="G31" s="4"/>
     </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="4"/>
+    </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
+      <c r="A34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C36" s="5">
-        <v>46089</v>
+        <v>46102</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="5">
-        <v>46090</v>
-      </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="7">
-        <v>46089</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="8"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A38" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46089</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="5">
-        <v>46085</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="5">
-        <v>46096</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="4"/>
+      <c r="A39" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="7">
-        <v>46089</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="A40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
-        <v>63</v>
+      <c r="A41" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4</v>
@@ -2405,362 +2477,512 @@
         <v>46089</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E41" s="5">
         <v>46090</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" s="5">
+      <c r="A42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="7">
         <v>46089</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="5">
-        <v>46090</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="D42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46096</v>
+      </c>
+      <c r="F42" s="22"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" s="5">
         <v>46089</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43" s="5">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C44" s="5">
-        <v>46089</v>
+        <v>46096</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E44" s="5">
-        <v>46090</v>
+        <v>46096</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="4" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A45" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="4" t="s">
+      <c r="A45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46089</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46096</v>
+      </c>
+      <c r="F45" s="23"/>
+      <c r="G45" s="8"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C46" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>46089</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="5">
+        <v>46090</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="5">
         <v>46096</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A46" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="32" t="s">
+      <c r="D50" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="5">
+        <v>46096</v>
+      </c>
+      <c r="F50" s="10"/>
+      <c r="G50" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C51" s="34">
         <v>46096</v>
       </c>
-      <c r="D46" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" s="30">
+      <c r="D51" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="38">
+        <v>46092</v>
+      </c>
+      <c r="F51" s="28"/>
+      <c r="G51" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="33">
         <v>46096</v>
       </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="29"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A47" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="38">
+      <c r="D52" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="33">
         <v>46096</v>
       </c>
-      <c r="D47" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="34">
+      <c r="F52" s="30"/>
+      <c r="G52" s="31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="17">
         <v>46096</v>
       </c>
-      <c r="F47" s="35"/>
-      <c r="G47" s="33"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A48" s="19" t="s">
+      <c r="D53" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="17">
+        <v>46096</v>
+      </c>
+      <c r="F53" s="24"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="17">
+        <v>46103</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="17"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="20"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="18">
-        <v>46096</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="17"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A49" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="18">
-        <v>46103</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="17"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A50" s="21"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="40"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="4"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="4"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="4"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A57" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="4"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A58" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="4"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A59" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
+      <c r="B59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E59" s="5"/>
       <c r="F59" s="10"/>
       <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A60" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
+      <c r="A60" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E60" s="5"/>
       <c r="F60" s="10"/>
       <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
+        <v>76</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E61" s="5"/>
       <c r="F61" s="10"/>
       <c r="G61" s="4"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A62" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
+      <c r="A62" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E62" s="5"/>
       <c r="F62" s="10"/>
       <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A63" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
+      <c r="A63" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E63" s="5"/>
       <c r="F63" s="10"/>
       <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A64" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
+      <c r="A64" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E64" s="5"/>
       <c r="F64" s="10"/>
       <c r="G64" s="4"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A65" s="20"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
+      <c r="A65" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E65" s="5"/>
       <c r="F65" s="10"/>
       <c r="G65" s="4"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
+      <c r="A66" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E66" s="5"/>
       <c r="F66" s="10"/>
       <c r="G66" s="4"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A67" s="19"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="25"/>
+      <c r="A67" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="10"/>
       <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A69" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="5">
+        <v>46102</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>

--- a/docs/Project 2 Plan.xlsx
+++ b/docs/Project 2 Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57bb492ad5be0872/Desktop/School/CS-2430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{F9671BB7-C4F0-4247-ABF4-8FE418D4BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A5445A-8D9B-4515-9419-6466EB63C29F}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A35F477B-69E0-4508-A779-2766FB3E9DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3072DF68-7313-4DFC-BC4F-F3A883A58564}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="1" activeTab="1" xr2:uid="{34D08FD4-51C7-4A98-AE26-ECA49DBE509F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="103">
   <si>
     <t>Group 2 Project 1: Set Operations</t>
   </si>
@@ -180,9 +180,6 @@
     <t>Individual</t>
   </si>
   <si>
-    <t>Incomplete</t>
-  </si>
-  <si>
     <t>Checkpoint</t>
   </si>
   <si>
@@ -325,6 +322,30 @@
   </si>
   <si>
     <t xml:space="preserve">    Screencast Brief Summary</t>
+  </si>
+  <si>
+    <t>Commit: 8dfb9ab2dbd0b928564f1b64efb2b5b00f3a7826</t>
+  </si>
+  <si>
+    <t>Commit: 1dfaf00be5cce80b0503e3197fed6785ad72c9cd</t>
+  </si>
+  <si>
+    <t>Commit: 97bd8cd7bc7709d04eaba924adf7d7da144f2d46</t>
+  </si>
+  <si>
+    <t>Commit: e498ba675921640d726b4f4e3584dc916b78c91a</t>
+  </si>
+  <si>
+    <t>Commit: cbee49782bce74e1aac0a84f2978de9e92ff2943</t>
+  </si>
+  <si>
+    <t>Commit: 3b5082e94c2c45e38a81edcc30bd1599c97cef68</t>
+  </si>
+  <si>
+    <t>Commit: db9f858b65b4748264e9546aa6c7957f68476f15</t>
+  </si>
+  <si>
+    <t>Commit: 2b8e3ceeb14ab68acd05f1a2cc19283b36dec617</t>
   </si>
 </sst>
 </file>
@@ -557,6 +578,7 @@
     <xf numFmtId="14" fontId="6" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -566,7 +588,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1336,10 +1357,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1747,25 +1764,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1845,37 +1862,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1884,15 +1901,15 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
@@ -1938,7 +1955,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
@@ -1957,7 +1974,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>46</v>
@@ -1976,7 +1993,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>46</v>
@@ -1985,15 +2002,17 @@
         <v>46103</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E10" s="5">
+        <v>46103</v>
+      </c>
       <c r="F10" s="21"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -2002,15 +2021,17 @@
         <v>46103</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E11" s="5">
+        <v>46105</v>
+      </c>
       <c r="F11" s="21"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>46</v>
@@ -2019,9 +2040,11 @@
         <v>46103</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46103</v>
+      </c>
       <c r="F12" s="10"/>
       <c r="G12" s="4"/>
     </row>
@@ -2034,15 +2057,15 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
@@ -2069,7 +2092,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>20</v>
@@ -2088,7 +2111,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>20</v>
@@ -2107,7 +2130,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
@@ -2141,12 +2164,12 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
@@ -2161,13 +2184,13 @@
         <v>46090</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>8</v>
@@ -2183,12 +2206,12 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
@@ -2203,7 +2226,7 @@
         <v>46096</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -2237,15 +2260,19 @@
         <v>46097</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E25" s="5">
+        <v>46097</v>
+      </c>
       <c r="F25" s="10"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>4</v>
@@ -2254,15 +2281,19 @@
         <v>46102</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E26" s="5">
+        <v>46102</v>
+      </c>
       <c r="F26" s="10"/>
-      <c r="G26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>20</v>
@@ -2271,7 +2302,7 @@
         <v>46102</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="22"/>
@@ -2279,7 +2310,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -2288,15 +2319,17 @@
         <v>46102</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E28" s="5">
+        <v>46105</v>
+      </c>
       <c r="F28" s="10"/>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>8</v>
@@ -2305,15 +2338,17 @@
         <v>46102</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E29" s="5">
+        <v>46102</v>
+      </c>
       <c r="F29" s="10"/>
       <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>8</v>
@@ -2322,15 +2357,17 @@
         <v>46102</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E30" s="5">
+        <v>46102</v>
+      </c>
       <c r="F30" s="10"/>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>4</v>
@@ -2339,15 +2376,17 @@
         <v>46102</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E31" s="5">
+        <v>46102</v>
+      </c>
       <c r="F31" s="10"/>
       <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>4</v>
@@ -2356,15 +2395,17 @@
         <v>46102</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E32" s="5">
+        <v>46102</v>
+      </c>
       <c r="F32" s="10"/>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>20</v>
@@ -2373,9 +2414,11 @@
         <v>46102</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E33" s="5">
+        <v>46103</v>
+      </c>
       <c r="F33" s="10"/>
       <c r="G33" s="4"/>
     </row>
@@ -2390,9 +2433,11 @@
         <v>46102</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E34" s="5">
+        <v>46104</v>
+      </c>
       <c r="F34" s="10"/>
       <c r="G34" s="4"/>
     </row>
@@ -2407,9 +2452,11 @@
         <v>46102</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E35" s="5">
+        <v>46103</v>
+      </c>
       <c r="F35" s="10"/>
       <c r="G35" s="4"/>
     </row>
@@ -2424,24 +2471,26 @@
         <v>46102</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E36" s="5">
+        <v>46102</v>
+      </c>
       <c r="F36" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
@@ -2468,7 +2517,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4</v>
@@ -2484,7 +2533,7 @@
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -2524,7 +2573,7 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
@@ -2545,7 +2594,7 @@
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
@@ -2553,7 +2602,7 @@
         <v>24</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" s="7">
         <v>46089</v>
@@ -2569,7 +2618,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>4</v>
@@ -2585,12 +2634,12 @@
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>4</v>
@@ -2606,12 +2655,12 @@
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>6</v>
@@ -2627,12 +2676,12 @@
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>6</v>
@@ -2648,7 +2697,7 @@
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
@@ -2669,12 +2718,12 @@
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>8</v>
@@ -2685,17 +2734,17 @@
       <c r="D51" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="38">
+      <c r="E51" s="35">
         <v>46092</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" s="31" t="s">
         <v>4</v>
@@ -2711,7 +2760,7 @@
       </c>
       <c r="F52" s="30"/>
       <c r="G52" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
@@ -2744,11 +2793,15 @@
         <v>46103</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E54" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="E54" s="17">
+        <v>46103</v>
+      </c>
       <c r="F54" s="24"/>
-      <c r="G54" s="16"/>
+      <c r="G54" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="20"/>
@@ -2757,15 +2810,15 @@
       <c r="E55" s="3"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
@@ -2801,15 +2854,19 @@
         <v>46102</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E59" s="5">
+        <v>46102</v>
+      </c>
       <c r="F59" s="10"/>
-      <c r="G59" s="4"/>
+      <c r="G59" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>8</v>
@@ -2818,15 +2875,19 @@
         <v>46102</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E60" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E60" s="5">
+        <v>46102</v>
+      </c>
       <c r="F60" s="10"/>
-      <c r="G60" s="4"/>
+      <c r="G60" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>8</v>
@@ -2835,11 +2896,15 @@
         <v>46102</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E61" s="5">
+        <v>46102</v>
+      </c>
       <c r="F61" s="10"/>
-      <c r="G61" s="4"/>
+      <c r="G61" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
@@ -2852,15 +2917,19 @@
         <v>46102</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E62" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E62" s="5">
+        <v>46102</v>
+      </c>
       <c r="F62" s="10"/>
-      <c r="G62" s="4"/>
+      <c r="G62" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>6</v>
@@ -2869,15 +2938,19 @@
         <v>46102</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E63" s="5">
+        <v>46102</v>
+      </c>
       <c r="F63" s="10"/>
-      <c r="G63" s="4"/>
+      <c r="G63" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>6</v>
@@ -2886,15 +2959,19 @@
         <v>46102</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E64" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E64" s="5">
+        <v>46103</v>
+      </c>
       <c r="F64" s="10"/>
-      <c r="G64" s="4"/>
+      <c r="G64" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>4</v>
@@ -2903,15 +2980,19 @@
         <v>46102</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E65" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E65" s="5">
+        <v>46102</v>
+      </c>
       <c r="F65" s="10"/>
-      <c r="G65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>4</v>
@@ -2920,15 +3001,19 @@
         <v>46102</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E66" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E66" s="5">
+        <v>46102</v>
+      </c>
       <c r="F66" s="10"/>
-      <c r="G66" s="4"/>
+      <c r="G66" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>6</v>
@@ -2937,15 +3022,19 @@
         <v>46102</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E67" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E67" s="5">
+        <v>46103</v>
+      </c>
       <c r="F67" s="10"/>
-      <c r="G67" s="4"/>
+      <c r="G67" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>8</v>
@@ -2954,15 +3043,19 @@
         <v>46102</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E68" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E68" s="5">
+        <v>46103</v>
+      </c>
       <c r="F68" s="10"/>
-      <c r="G68" s="4"/>
+      <c r="G68" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>8</v>
@@ -2971,11 +3064,15 @@
         <v>46102</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E69" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="E69" s="5">
+        <v>46103</v>
+      </c>
       <c r="F69" s="10"/>
-      <c r="G69" s="4"/>
+      <c r="G69" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
